--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486313_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486313_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0356</v>
+        <v>4.5407</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2604</v>
+        <v>2.9504</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7752</v>
+        <v>1.5903</v>
       </c>
       <c r="G2" t="n">
         <v>2.7066</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6542</v>
+        <v>0.1592</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.5876</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2435</v>
+        <v>-0.4284</v>
       </c>
       <c r="V2" t="n">
         <v>0.3698</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9819</v>
+        <v>4.5272</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3924</v>
+        <v>2.7218</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5896</v>
+        <v>1.8053</v>
       </c>
       <c r="G3" t="n">
         <v>2.6841</v>
@@ -688,13 +688,13 @@
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0379</v>
+        <v>0.5831</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2966</v>
+        <v>0.6261</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2587</v>
+        <v>-0.043</v>
       </c>
       <c r="V3" t="n">
         <v>1.695</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4163</v>
+        <v>4.1946</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6096</v>
+        <v>2.6982</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8067</v>
+        <v>1.4964</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9866</v>
+        <v>1.5077</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2232</v>
+        <v>0.298</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7634</v>
+        <v>1.2096</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2313</v>
+        <v>1.9309</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1931</v>
+        <v>0.5324</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0382</v>
+        <v>1.3985</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7553</v>
+        <v>-0.4233</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0302</v>
+        <v>-0.2344</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7251</v>
+        <v>-0.1889</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5225</v>
+        <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9522</v>
+        <v>-0.313</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2281</v>
+        <v>0.1598</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2759</v>
+        <v>-0.4729</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>1.695</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8939</v>
+        <v>3.9808</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8592</v>
+        <v>2.0508</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0347</v>
+        <v>1.93</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3901</v>
+        <v>2.9866</v>
       </c>
       <c r="H5" t="n">
-        <v>2.418</v>
+        <v>2.2232</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0279</v>
+        <v>0.7634</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5798</v>
+        <v>2.2313</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5033</v>
+        <v>2.1931</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0765</v>
+        <v>0.0382</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1898</v>
+        <v>0.7553</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0854</v>
+        <v>0.0302</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1044</v>
+        <v>0.7251</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6525</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.5167</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1717</v>
+        <v>0.6694</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3204</v>
+        <v>-0.1526</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="X5" t="n">
         <v>-0.1952</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6838</v>
+        <v>3.3033</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0024</v>
+        <v>2.1454</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6814</v>
+        <v>1.158</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5077</v>
+        <v>2.3901</v>
       </c>
       <c r="H6" t="n">
-        <v>0.298</v>
+        <v>2.418</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2096</v>
+        <v>-0.0279</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9309</v>
+        <v>2.5798</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5324</v>
+        <v>2.5033</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3985</v>
+        <v>0.0765</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4233</v>
+        <v>-0.1898</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2344</v>
+        <v>-0.0854</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1889</v>
+        <v>-0.1044</v>
       </c>
       <c r="P6" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3926</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8239</v>
+        <v>0.2608</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.536</v>
+        <v>0.4579</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2879</v>
+        <v>-0.1971</v>
       </c>
       <c r="V6" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.695</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.3367</v>
+        <v>3.2888</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2553</v>
+        <v>2.3923</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0814</v>
+        <v>0.8964</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0004</v>
@@ -1000,13 +1000,13 @@
         <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0103</v>
+        <v>-0.0583</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2776</v>
+        <v>0.4146</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2879</v>
+        <v>-0.4729</v>
       </c>
       <c r="V7" t="n">
         <v>2.2599</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6567</v>
+        <v>2.2656</v>
       </c>
       <c r="E8" t="n">
-        <v>0.738</v>
+        <v>1.4085</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9187</v>
+        <v>0.8571</v>
       </c>
       <c r="G8" t="n">
         <v>1.8917</v>
@@ -1078,13 +1078,13 @@
         <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.1688</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3184</v>
+        <v>0.3521</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4593</v>
+        <v>-0.521</v>
       </c>
       <c r="V8" t="n">
         <v>0.7602</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2453</v>
+        <v>1.4958</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4804</v>
+        <v>0.0784</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7257</v>
+        <v>1.4175</v>
       </c>
       <c r="G9" t="n">
         <v>0.2228</v>
@@ -1156,13 +1156,13 @@
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2824</v>
+        <v>0.5329</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1815</v>
+        <v>0.3773</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4638</v>
+        <v>0.1556</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5649999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7602</v>
+        <v>1.4731</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9443</v>
+        <v>-0.3855</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7045</v>
+        <v>1.8586</v>
       </c>
       <c r="G10" t="n">
         <v>0.9898</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0102</v>
+        <v>0.7231</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1815</v>
+        <v>0.3773</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1917</v>
+        <v>0.3458</v>
       </c>
       <c r="V10" t="n">
         <v>0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.27</v>
+        <v>0.3509</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.169</v>
+        <v>-0.0572</v>
       </c>
       <c r="F11" t="n">
-        <v>0.439</v>
+        <v>0.4082</v>
       </c>
       <c r="G11" t="n">
         <v>0.3831</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3306</v>
+        <v>-0.2497</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1251</v>
+        <v>-0.1559</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6358</v>
+        <v>-1.1696</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.118</v>
+        <v>0.7211</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5178</v>
+        <v>-1.8908</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.2488</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3528</v>
+        <v>1.2955</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-1.5443</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1695</v>
+        <v>1.0861</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0547</v>
+        <v>1.314</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1147</v>
+        <v>-0.2279</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7849</v>
+        <v>-1.3348</v>
       </c>
       <c r="N12" t="n">
-        <v>0.298</v>
+        <v>-0.0184</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0829</v>
+        <v>-1.3164</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1542</v>
+        <v>-0.0312</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5396</v>
+        <v>0.0048</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3854</v>
+        <v>-0.0361</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7395</v>
+        <v>-2.6297</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7395</v>
+        <v>-0.3698</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8885</v>
+        <v>-1.8101</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2489</v>
+        <v>-1.3848</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1374</v>
+        <v>-0.4253</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2488</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2955</v>
+        <v>0.3528</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.5443</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0861</v>
+        <v>0.1695</v>
       </c>
       <c r="K13" t="n">
-        <v>1.314</v>
+        <v>0.0547</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2279</v>
+        <v>0.1147</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3348</v>
+        <v>-0.7849</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0184</v>
+        <v>0.298</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3164</v>
+        <v>-1.0829</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7401</v>
+        <v>-0.435</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7501</v>
+        <v>-0.0201</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4675</v>
+        <v>0.2728</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2826</v>
+        <v>-0.2929</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.6297</v>
+        <v>-0.7395</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3698</v>
+        <v>-0.7395</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.7561</v>
+        <v>26.4411</v>
       </c>
       <c r="E14" t="n">
-        <v>14.6545</v>
+        <v>15.3394</v>
       </c>
       <c r="F14" t="n">
         <v>11.1017</v>
@@ -1516,7 +1516,7 @@
         <v>15.4199</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5220999999999998</v>
+        <v>-0.5221000000000002</v>
       </c>
       <c r="J14" t="n">
         <v>15.9948</v>
@@ -1546,13 +1546,13 @@
         <v>19.5758</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2498</v>
+        <v>1.9347</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5209</v>
+        <v>4.206</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.2712</v>
+        <v>-2.2714</v>
       </c>
       <c r="V14" t="n">
         <v>4.1709</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6823</v>
+        <v>2.1042</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8659</v>
+        <v>0.7483</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8164</v>
+        <v>1.3559</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2123</v>
@@ -1624,13 +1624,13 @@
         <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7418</v>
+        <v>0.1637</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3808</v>
+        <v>0.2632</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6389</v>
+        <v>-0.0994</v>
       </c>
       <c r="V15" t="n">
         <v>0.1952</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2829</v>
+        <v>1.0286</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3653</v>
+        <v>2.1418</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0824</v>
+        <v>-1.1133</v>
       </c>
       <c r="G16" t="n">
         <v>0.0468</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>0.346</v>
+        <v>0.0916</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7006</v>
+        <v>0.4771</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3546</v>
+        <v>-0.3854</v>
       </c>
       <c r="V16" t="n">
         <v>1.3252</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>M. JACKSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1274</v>
+        <v>0.5492</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9484</v>
+        <v>-0.2069</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.821</v>
+        <v>0.7561</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1172</v>
+        <v>0.8149</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8972</v>
+        <v>-2.6458</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0144</v>
+        <v>3.4608</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9811</v>
+        <v>2.9476</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8281</v>
+        <v>-0.5531</v>
       </c>
       <c r="L17" t="n">
-        <v>0.153</v>
+        <v>3.5006</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0983</v>
+        <v>-2.1327</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-2.0928</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1674</v>
+        <v>-0.0399</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.8276</v>
+        <v>-0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4801</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>2.3926</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1375</v>
+        <v>-0.1352</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1222</v>
+        <v>0.1082</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0153</v>
+        <v>-0.2434</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9347</v>
+        <v>0.7395</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3904</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. JACKSON</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-1.3061</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1009</v>
+        <v>0.6073</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1498</v>
+        <v>-1.9134</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8149</v>
+        <v>-0.1172</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.6458</v>
+        <v>0.8972</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4608</v>
+        <v>-1.0144</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9476</v>
+        <v>1.9811</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5531</v>
+        <v>1.8281</v>
       </c>
       <c r="L18" t="n">
-        <v>3.5006</v>
+        <v>0.153</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1327</v>
+        <v>-2.0983</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0928</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0399</v>
+        <v>-1.1674</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.87</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2626</v>
+        <v>-3.4801</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3926</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6355</v>
+        <v>0.7039</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7859</v>
+        <v>0.7811</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8496</v>
+        <v>-0.0772</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7395</v>
+        <v>0.9347</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X18" t="n">
-        <v>0.7395</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1271</v>
+        <v>-1.7089</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5909</v>
+        <v>-0.8159</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5363</v>
+        <v>-0.893</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-1.3643</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6093</v>
+        <v>-1.177</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9021</v>
+        <v>-0.1873</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4061</v>
+        <v>-0.596</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.049</v>
+        <v>-0.5776</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4551</v>
+        <v>-0.0183</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1134</v>
+        <v>-0.7683</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5604</v>
+        <v>-0.5994</v>
       </c>
       <c r="O19" t="n">
-        <v>0.447</v>
+        <v>-0.1689</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4846</v>
+        <v>-0.1069</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1694</v>
+        <v>-0.2199</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3152</v>
+        <v>0.113</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3698</v>
+        <v>-1.3252</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1947</v>
+        <v>-1.7169</v>
       </c>
       <c r="E20" t="n">
         <v>-2.8194</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6247</v>
+        <v>1.1026</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3933</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3664</v>
+        <v>0.1115</v>
       </c>
       <c r="T20" t="n">
         <v>0.1646</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.531</v>
+        <v>-0.0532</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.924</v>
+        <v>-2.1079</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4864</v>
+        <v>-1.4791</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4376</v>
+        <v>-0.6287</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3643</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.177</v>
+        <v>-2.6093</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1873</v>
+        <v>1.9021</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.596</v>
+        <v>0.4061</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5776</v>
+        <v>-1.049</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0183</v>
+        <v>1.4551</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7683</v>
+        <v>-1.1134</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5994</v>
+        <v>-1.5604</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1689</v>
+        <v>0.447</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R21" t="n">
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3221</v>
+        <v>-0.4654</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8904</v>
+        <v>-0.0577</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4317</v>
+        <v>-0.4077</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3252</v>
+        <v>0.3698</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0705</v>
+        <v>-2.382</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0574</v>
+        <v>0.3896</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0131</v>
+        <v>-2.7717</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9712</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5344</v>
+        <v>0.1541</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1815</v>
+        <v>0.2656</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3529</v>
+        <v>-0.1115</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>A. ALONSO CUEVAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6588</v>
+        <v>-3.0268</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.7326</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7853</v>
+        <v>-2.2942</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8183</v>
+        <v>-0.5897</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4119</v>
+        <v>-1.3627</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4064</v>
+        <v>0.773</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4061</v>
+        <v>0.6926</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.3983</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2295</v>
+        <v>1.0909</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4123</v>
+        <v>-1.2823</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7764</v>
+        <v>-0.9643</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6359</v>
+        <v>-0.318</v>
       </c>
       <c r="P23" t="n">
-        <v>1.0875</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.233</v>
+        <v>-0.4593</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4675</v>
+        <v>-0.1202</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2344</v>
+        <v>-0.3392</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.695</v>
+        <v>-1.3252</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.695</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ALONSO CUEVAS</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8142</v>
+        <v>-3.4892</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0679</v>
+        <v>-0.4265</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7463</v>
+        <v>-3.0627</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5897</v>
+        <v>-2.8183</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.3627</v>
+        <v>-2.4119</v>
       </c>
       <c r="I24" t="n">
-        <v>0.773</v>
+        <v>-0.4064</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6926</v>
+        <v>-0.4061</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3983</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>1.0909</v>
+        <v>0.2295</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2823</v>
+        <v>-2.4123</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9643</v>
+        <v>-1.7764</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.318</v>
+        <v>-0.6359</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2468</v>
+        <v>-0.0634</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4554</v>
+        <v>-0.0204</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7913</v>
+        <v>-0.043</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.3252</v>
+        <v>-1.695</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3252</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>A. ALONSO RUIZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2999</v>
+        <v>-5.4666</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6115</v>
+        <v>-3.4499</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6884</v>
+        <v>-2.0168</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.9663</v>
+        <v>-0.6197</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.3455</v>
+        <v>0.0608</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.6208</v>
+        <v>-0.6805</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.2656</v>
+        <v>-0.4348</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.8337</v>
+        <v>0.3102</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.4319</v>
+        <v>-0.7451</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7007</v>
+        <v>-0.1849</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.5118</v>
+        <v>-0.2495</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1889</v>
+        <v>0.0645</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6525</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S25" t="n">
-        <v>1.4489</v>
+        <v>0.2406</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8292</v>
+        <v>0.2476</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6197</v>
+        <v>-0.0069</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. ALONSO RUIZ</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.8083</v>
+        <v>-5.9986</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6734</v>
+        <v>-5.0585</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.135</v>
+        <v>-0.9401</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6197</v>
+        <v>-4.9663</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0608</v>
+        <v>-3.3455</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6805</v>
+        <v>-1.6208</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4348</v>
+        <v>-3.2656</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3102</v>
+        <v>-1.8337</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.7451</v>
+        <v>-1.4319</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1849</v>
+        <v>-1.7007</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2495</v>
+        <v>-1.5118</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0645</v>
+        <v>-0.1889</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.8276</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R26" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1011</v>
+        <v>0.7502</v>
       </c>
       <c r="T26" t="n">
-        <v>0.024</v>
+        <v>0.3822</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1251</v>
+        <v>0.368</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-25.756</v>
+        <v>-23.521</v>
       </c>
       <c r="E27" t="n">
-        <v>-11.1017</v>
+        <v>-11.1018</v>
       </c>
       <c r="F27" t="n">
-        <v>-14.6545</v>
+        <v>-12.4193</v>
       </c>
       <c r="G27" t="n">
         <v>-14.8978</v>
@@ -2530,10 +2530,10 @@
         <v>-15.4199</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5221000000000003</v>
+        <v>0.5221000000000005</v>
       </c>
       <c r="J27" t="n">
-        <v>1.097</v>
+        <v>1.096999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>-1.2143</v>
@@ -2560,13 +2560,13 @@
         <v>14.1378</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.2497</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2713</v>
+        <v>2.2714</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.5209</v>
+        <v>-1.2859</v>
       </c>
       <c r="V27" t="n">
         <v>-4.1709</v>
